--- a/ruoyi-admin/src/main/resources/template/排污许可列表模版.xlsx
+++ b/ruoyi-admin/src/main/resources/template/排污许可列表模版.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
-    <sheet name="排污许可统计表" sheetId="1" r:id="rId1"/>
+    <sheet name="排污许可列表" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
   <si>
     <t>排污许可统计表</t>
   </si>
@@ -38,9 +38,6 @@
     <t>企业名称</t>
   </si>
   <si>
-    <t>持证单位名称</t>
-  </si>
-  <si>
     <t>社会信用代码</t>
   </si>
   <si>
@@ -65,13 +62,7 @@
     <t>主要产品</t>
   </si>
   <si>
-    <t>产量(台)</t>
-  </si>
-  <si>
-    <t>平台账号</t>
-  </si>
-  <si>
-    <t>密码</t>
+    <t>产量</t>
   </si>
   <si>
     <t>大气</t>
@@ -1328,15 +1319,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="15" max="20" width="30" customWidth="1"/>
+    <col min="1" max="1" width="10.3333333333333" customWidth="1"/>
+    <col min="2" max="2" width="31.5555555555556" customWidth="1"/>
+    <col min="3" max="3" width="30.8888888888889" customWidth="1"/>
+    <col min="4" max="4" width="27.8888888888889" customWidth="1"/>
+    <col min="5" max="5" width="22.6666666666667" customWidth="1"/>
+    <col min="6" max="6" width="23.3333333333333" customWidth="1"/>
+    <col min="7" max="7" width="22.7777777777778" customWidth="1"/>
+    <col min="8" max="8" width="14.6666666666667" customWidth="1"/>
+    <col min="9" max="9" width="29.4444444444444" customWidth="1"/>
+    <col min="10" max="10" width="25.4444444444444" customWidth="1"/>
+    <col min="11" max="11" width="26.7777777777778" customWidth="1"/>
+    <col min="12" max="17" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.2" spans="1:21">
+    <row r="1" ht="19.2" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1357,11 +1357,8 @@
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
     </row>
-    <row r="2" ht="35" customHeight="1" spans="1:21">
+    <row r="2" ht="35" customHeight="1" spans="1:18">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1402,94 +1399,76 @@
         <v>13</v>
       </c>
       <c r="N2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>18</v>
-      </c>
     </row>
-    <row r="3" ht="35" customHeight="1" spans="1:21">
+    <row r="3" ht="35" customHeight="1" spans="1:18">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>16</v>
       </c>
       <c r="M3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="P3" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
-    <row r="4" ht="25" customHeight="1" spans="1:21">
+    <row r="4" ht="25" customHeight="1" spans="1:18">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1508,15 +1487,12 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="U4" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A1:U1"/>
+  <mergeCells count="15">
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -1528,10 +1504,7 @@
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="R2:R3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
